--- a/public/templates/plantilla_pensum.xlsx
+++ b/public/templates/plantilla_pensum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Proyect-E\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B244C6-1857-4519-AD2A-5559705226F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023C8381-3435-4456-BADD-51C654D5A41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="3075" windowWidth="16410" windowHeight="14145" xr2:uid="{9475300B-540A-4F31-A558-60C66FB74412}"/>
+    <workbookView xWindow="28680" yWindow="-11085" windowWidth="16440" windowHeight="28320" xr2:uid="{9475300B-540A-4F31-A558-60C66FB74412}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
